--- a/example/assets/samples/sales.xlsx
+++ b/example/assets/samples/sales.xlsx
@@ -490,8 +490,11 @@
   <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -632,13 +635,11 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B8" s="4">
-        <f>SUM(B2:B6)</f>
-        <v/>
-      </c>
-      <c r="C8" s="4">
-        <f>SUM(C2:C6)</f>
-        <v/>
+      <c r="B8" s="4" t="n">
+        <v>485</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>505</v>
       </c>
       <c r="D8" s="4" t="n"/>
       <c r="E8" s="4" t="n"/>
